--- a/Assets/Originals/Excels/System/SystemMessage.xlsx
+++ b/Assets/Originals/Excels/System/SystemMessage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8207965-25A2-4A24-93E6-2FB6C69D9E8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{277C20D5-FE25-463F-929D-2A51F1B03543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="119">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -443,6 +443,60 @@
   <si>
     <t>这里是常世</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>messageRussian</t>
+  </si>
+  <si>
+    <t>messageSizeRussian</t>
+  </si>
+  <si>
+    <t>Здесь — Вечный мир</t>
+  </si>
+  <si>
+    <t>Мир, куда попадают те,
+кто умер в мире живых</t>
+  </si>
+  <si>
+    <t>Назовите имя, которое вы носили
+в мире живых</t>
+  </si>
+  <si>
+    <t>Введите от 2 до 10 символов</t>
+  </si>
+  <si>
+    <t>Благодарю вас</t>
+  </si>
+  <si>
+    <t>А теперь… ваше имя я здесь же…</t>
+  </si>
+  <si>
+    <t>…уничтожаю</t>
+  </si>
+  <si>
+    <t>Начинается обучение</t>
+  </si>
+  <si>
+    <t>Управляйте персонажем
+и откройте ящик левой кнопкой мыши</t>
+  </si>
+  <si>
+    <t>Нажмите P, Z или ESC, чтобы открыть меню паузы → «Предметы»
+→ «Документы» → «Обучение»</t>
+  </si>
+  <si>
+    <t>ЛКМ… открыть ящик</t>
+  </si>
+  <si>
+    <t>Нажмите P, Z или ESC, чтобы открыть меню паузы → «Предметы»
+→ «Загадочные предметы» → «Молоток» или «Верёвка»</t>
+  </si>
+  <si>
+    <t>ЛКМ… коснуться Синей сферы Правосудия
+Выберите изображение загадочного предмета ЛКМ</t>
+  </si>
+  <si>
+    <t>Обучение завершено</t>
   </si>
 </sst>
 </file>
@@ -796,7 +850,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S52"/>
+  <dimension ref="A1:U52"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="114.5" customWidth="1"/>
@@ -807,15 +861,17 @@
     <col min="7" max="11" width="26.625" customWidth="1"/>
     <col min="12" max="12" width="21.5" customWidth="1"/>
     <col min="13" max="13" width="27.875" customWidth="1"/>
-    <col min="14" max="14" width="27.25" customWidth="1"/>
-    <col min="15" max="15" width="26.625" customWidth="1"/>
-    <col min="16" max="16" width="22.25" customWidth="1"/>
-    <col min="17" max="17" width="23.875" customWidth="1"/>
-    <col min="18" max="18" width="24.125" customWidth="1"/>
-    <col min="19" max="19" width="14.625" customWidth="1"/>
+    <col min="14" max="14" width="79.375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20.625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="27.25" customWidth="1"/>
+    <col min="17" max="17" width="26.625" customWidth="1"/>
+    <col min="18" max="18" width="22.25" customWidth="1"/>
+    <col min="19" max="19" width="23.875" customWidth="1"/>
+    <col min="20" max="20" width="24.125" customWidth="1"/>
+    <col min="21" max="21" width="14.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:21">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -856,25 +912,31 @@
         <v>82</v>
       </c>
       <c r="N1" t="s">
+        <v>103</v>
+      </c>
+      <c r="O1" t="s">
+        <v>104</v>
+      </c>
+      <c r="P1" t="s">
         <v>1</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>2</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>3</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>4</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
         <v>5</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:21">
       <c r="A2">
         <v>0</v>
       </c>
@@ -885,12 +947,6 @@
       <c r="E2">
         <v>0</v>
       </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
       <c r="P2">
         <v>0</v>
       </c>
@@ -903,8 +959,14 @@
       <c r="S2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:19">
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21">
       <c r="A3">
         <v>1</v>
       </c>
@@ -944,11 +1006,11 @@
       <c r="M3">
         <v>32</v>
       </c>
-      <c r="N3">
-        <v>0</v>
+      <c r="N3" s="2" t="s">
+        <v>105</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="P3">
         <v>0</v>
@@ -962,8 +1024,14 @@
       <c r="S3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:19" ht="56.25">
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" ht="75">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1003,11 +1071,11 @@
       <c r="M4">
         <v>24</v>
       </c>
-      <c r="N4">
-        <v>0</v>
+      <c r="N4" s="3" t="s">
+        <v>106</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -1021,8 +1089,14 @@
       <c r="S4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:19" ht="37.5">
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" ht="37.5">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1062,15 +1136,15 @@
       <c r="M5">
         <v>24</v>
       </c>
-      <c r="N5">
+      <c r="N5" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="O5">
+        <v>24</v>
+      </c>
+      <c r="P5">
         <v>1</v>
       </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>0</v>
-      </c>
       <c r="Q5">
         <v>0</v>
       </c>
@@ -1080,8 +1154,14 @@
       <c r="S5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:19" ht="37.5">
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="37.5">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1121,26 +1201,32 @@
       <c r="M6">
         <v>24</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="O6">
+        <v>24</v>
+      </c>
+      <c r="P6">
         <v>2</v>
       </c>
-      <c r="O6">
+      <c r="Q6">
         <v>3</v>
       </c>
-      <c r="P6">
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
       <c r="R6">
         <v>0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:19">
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1180,11 +1266,11 @@
       <c r="M7">
         <v>32</v>
       </c>
-      <c r="N7">
-        <v>0</v>
+      <c r="N7" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -1198,8 +1284,14 @@
       <c r="S7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:19">
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1239,26 +1331,32 @@
       <c r="M8">
         <v>32</v>
       </c>
-      <c r="N8">
-        <v>0</v>
+      <c r="N8" s="2" t="s">
+        <v>110</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
         <v>3</v>
       </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
       <c r="S8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:19">
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1298,11 +1396,11 @@
       <c r="M9">
         <v>32</v>
       </c>
-      <c r="N9">
-        <v>0</v>
+      <c r="N9" s="2" t="s">
+        <v>111</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -1316,8 +1414,14 @@
       <c r="S9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:19">
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1328,12 +1432,6 @@
       <c r="E10">
         <v>0</v>
       </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
       <c r="P10">
         <v>0</v>
       </c>
@@ -1346,8 +1444,14 @@
       <c r="S10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:19">
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1387,26 +1491,32 @@
       <c r="M11" s="1">
         <v>22</v>
       </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11">
-        <v>0</v>
+      <c r="N11" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="O11" s="1">
+        <v>22</v>
       </c>
       <c r="P11">
         <v>0</v>
       </c>
       <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
         <v>1</v>
       </c>
-      <c r="R11">
+      <c r="T11">
         <v>38</v>
       </c>
-      <c r="S11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" ht="75">
+      <c r="U11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" ht="93.75">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1446,11 +1556,11 @@
       <c r="M12" s="1">
         <v>22</v>
       </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12">
-        <v>0</v>
+      <c r="N12" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="O12" s="1">
+        <v>22</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -1459,13 +1569,19 @@
         <v>0</v>
       </c>
       <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
         <v>43</v>
       </c>
-      <c r="S12">
+      <c r="U12">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="112.5">
+    <row r="13" spans="1:21" ht="131.25">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1505,11 +1621,11 @@
       <c r="M13" s="1">
         <v>22</v>
       </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13">
-        <v>0</v>
+      <c r="N13" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="O13" s="1">
+        <v>22</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -1518,13 +1634,19 @@
         <v>0</v>
       </c>
       <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
         <v>44</v>
       </c>
-      <c r="S13">
+      <c r="U13">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="37.5">
+    <row r="14" spans="1:21" ht="37.5">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1564,11 +1686,11 @@
       <c r="M14" s="1">
         <v>22</v>
       </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14">
-        <v>0</v>
+      <c r="N14" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="O14" s="1">
+        <v>22</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -1577,13 +1699,19 @@
         <v>0</v>
       </c>
       <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
         <v>46</v>
       </c>
-      <c r="S14">
+      <c r="U14">
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="112.5">
+    <row r="15" spans="1:21" ht="168.75">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1623,11 +1751,11 @@
       <c r="M15" s="1">
         <v>22</v>
       </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15">
-        <v>0</v>
+      <c r="N15" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="O15" s="1">
+        <v>22</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -1636,13 +1764,19 @@
         <v>0</v>
       </c>
       <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
         <v>47</v>
       </c>
-      <c r="S15">
+      <c r="U15">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="131.25">
+    <row r="16" spans="1:21" ht="168.75">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1682,11 +1816,11 @@
       <c r="M16" s="1">
         <v>22</v>
       </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16">
-        <v>0</v>
+      <c r="N16" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="O16" s="1">
+        <v>22</v>
       </c>
       <c r="P16">
         <v>0</v>
@@ -1698,10 +1832,16 @@
         <v>0</v>
       </c>
       <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:19">
+    <row r="17" spans="1:21" ht="37.5">
       <c r="A17">
         <v>15</v>
       </c>
@@ -1741,26 +1881,32 @@
       <c r="M17" s="1">
         <v>22</v>
       </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
-      <c r="O17">
-        <v>0</v>
+      <c r="N17" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="O17" s="1">
+        <v>22</v>
       </c>
       <c r="P17">
         <v>0</v>
       </c>
       <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
         <v>2</v>
       </c>
-      <c r="R17">
+      <c r="T17">
         <v>49</v>
       </c>
-      <c r="S17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19">
+      <c r="U17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1776,8 +1922,10 @@
       <c r="K18" s="5"/>
       <c r="L18" s="1"/>
       <c r="M18" s="5"/>
-    </row>
-    <row r="19" spans="1:19">
+      <c r="N18" s="1"/>
+      <c r="O18" s="5"/>
+    </row>
+    <row r="19" spans="1:21">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1786,67 +1934,67 @@
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
     </row>
-    <row r="20" spans="1:19">
+    <row r="20" spans="1:21">
       <c r="A20">
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:19">
+    <row r="21" spans="1:21">
       <c r="A21">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:19">
+    <row r="22" spans="1:21">
       <c r="A22">
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:19">
+    <row r="23" spans="1:21">
       <c r="A23">
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:19">
+    <row r="24" spans="1:21">
       <c r="A24">
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:19">
+    <row r="25" spans="1:21">
       <c r="A25">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:19">
+    <row r="26" spans="1:21">
       <c r="A26">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:19">
+    <row r="27" spans="1:21">
       <c r="A27">
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:19">
+    <row r="28" spans="1:21">
       <c r="A28">
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:19">
+    <row r="29" spans="1:21">
       <c r="A29">
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:19">
+    <row r="30" spans="1:21">
       <c r="A30">
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:19">
+    <row r="31" spans="1:21">
       <c r="A31">
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:19">
+    <row r="32" spans="1:21">
       <c r="A32">
         <v>30</v>
       </c>

--- a/Assets/Originals/Excels/System/SystemMessage.xlsx
+++ b/Assets/Originals/Excels/System/SystemMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{277C20D5-FE25-463F-929D-2A51F1B03543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD80C577-EE33-4EC7-8EAC-BBD053C29D49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="135">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -497,6 +497,60 @@
   </si>
   <si>
     <t>Обучение завершено</t>
+  </si>
+  <si>
+    <t>messageGerman</t>
+  </si>
+  <si>
+    <t>messageSizeGerman</t>
+  </si>
+  <si>
+    <t>Dies ist die Ewige Welt</t>
+  </si>
+  <si>
+    <t>Die Welt, in die jene gelangen,
+die in der Welt der Lebenden gestorben sind</t>
+  </si>
+  <si>
+    <t>Bitte nenne mir den Namen,
+den du in der Welt der Lebenden getragen hast</t>
+  </si>
+  <si>
+    <t>Gib einen Namen mit 2 bis 10 Zeichen ein</t>
+  </si>
+  <si>
+    <t>Vielen Dank, dass du ihn mir verraten hast</t>
+  </si>
+  <si>
+    <t>Nun denn … deinen Namen werde ich hier und jetzt …</t>
+  </si>
+  <si>
+    <t>… vernichten</t>
+  </si>
+  <si>
+    <t>Das Tutorial beginnt</t>
+  </si>
+  <si>
+    <t>Bewege die Spielfigur und
+öffne die Schublade mit einem Linksklick</t>
+  </si>
+  <si>
+    <t>Öffne mit P, Z oder ESC das Pausenmenü → „Gegenstände“
+→ „Dokumente“ → „Tutorial“</t>
+  </si>
+  <si>
+    <t>Linksklick … Schublade öffnen</t>
+  </si>
+  <si>
+    <t>Öffne mit P, Z oder ESC das Pausenmenü → „Gegenstände“
+→ „Mysteriöse Gegenstände“ → „Hammer“ oder „Seil“</t>
+  </si>
+  <si>
+    <t>Linksklick … die Blaue Kugel des Urteils berühren
+Wähle das Bild des Mysteriösen Gegenstands per Linksklick</t>
+  </si>
+  <si>
+    <t>Das Tutorial ist beendet</t>
   </si>
 </sst>
 </file>
@@ -850,7 +904,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U52"/>
+  <dimension ref="A1:W52"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="114.5" customWidth="1"/>
@@ -863,15 +917,17 @@
     <col min="13" max="13" width="27.875" customWidth="1"/>
     <col min="14" max="14" width="79.375" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="20.625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="27.25" customWidth="1"/>
-    <col min="17" max="17" width="26.625" customWidth="1"/>
-    <col min="18" max="18" width="22.25" customWidth="1"/>
-    <col min="19" max="19" width="23.875" customWidth="1"/>
-    <col min="20" max="20" width="24.125" customWidth="1"/>
-    <col min="21" max="21" width="14.625" customWidth="1"/>
+    <col min="16" max="16" width="71.75" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20.375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="27.25" customWidth="1"/>
+    <col min="19" max="19" width="26.625" customWidth="1"/>
+    <col min="20" max="20" width="22.25" customWidth="1"/>
+    <col min="21" max="21" width="23.875" customWidth="1"/>
+    <col min="22" max="22" width="24.125" customWidth="1"/>
+    <col min="23" max="23" width="14.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21">
+    <row r="1" spans="1:23">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -918,25 +974,31 @@
         <v>104</v>
       </c>
       <c r="P1" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>120</v>
+      </c>
+      <c r="R1" t="s">
         <v>1</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>2</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
         <v>3</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
         <v>4</v>
       </c>
-      <c r="T1" t="s">
+      <c r="V1" t="s">
         <v>5</v>
       </c>
-      <c r="U1" t="s">
+      <c r="W1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:23">
       <c r="A2">
         <v>0</v>
       </c>
@@ -947,12 +1009,6 @@
       <c r="E2">
         <v>0</v>
       </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
       <c r="R2">
         <v>0</v>
       </c>
@@ -965,8 +1021,14 @@
       <c r="U2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:21">
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1012,11 +1074,11 @@
       <c r="O3">
         <v>32</v>
       </c>
-      <c r="P3">
-        <v>0</v>
+      <c r="P3" s="2" t="s">
+        <v>121</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -1030,8 +1092,14 @@
       <c r="U3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:21" ht="75">
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" ht="93.75">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1077,11 +1145,11 @@
       <c r="O4">
         <v>24</v>
       </c>
-      <c r="P4">
-        <v>0</v>
+      <c r="P4" s="3" t="s">
+        <v>122</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -1095,8 +1163,14 @@
       <c r="U4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:21" ht="37.5">
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" ht="37.5">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1142,15 +1216,15 @@
       <c r="O5">
         <v>24</v>
       </c>
-      <c r="P5">
+      <c r="P5" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q5">
+        <v>24</v>
+      </c>
+      <c r="R5">
         <v>1</v>
       </c>
-      <c r="Q5">
-        <v>0</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
       <c r="S5">
         <v>0</v>
       </c>
@@ -1160,8 +1234,14 @@
       <c r="U5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:21" ht="37.5">
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" ht="37.5">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1207,26 +1287,32 @@
       <c r="O6">
         <v>24</v>
       </c>
-      <c r="P6">
+      <c r="P6" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q6">
+        <v>24</v>
+      </c>
+      <c r="R6">
         <v>2</v>
       </c>
-      <c r="Q6">
+      <c r="S6">
         <v>3</v>
       </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
       <c r="T6">
         <v>0</v>
       </c>
       <c r="U6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:21">
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1272,11 +1358,11 @@
       <c r="O7">
         <v>32</v>
       </c>
-      <c r="P7">
-        <v>0</v>
+      <c r="P7" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -1290,8 +1376,14 @@
       <c r="U7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:21">
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1337,26 +1429,32 @@
       <c r="O8">
         <v>32</v>
       </c>
-      <c r="P8">
-        <v>0</v>
+      <c r="P8" s="2" t="s">
+        <v>126</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
         <v>3</v>
       </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
       <c r="U8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:21">
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1402,11 +1500,11 @@
       <c r="O9">
         <v>32</v>
       </c>
-      <c r="P9">
-        <v>0</v>
+      <c r="P9" s="2" t="s">
+        <v>127</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -1420,8 +1518,14 @@
       <c r="U9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:21">
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1432,12 +1536,6 @@
       <c r="E10">
         <v>0</v>
       </c>
-      <c r="P10">
-        <v>0</v>
-      </c>
-      <c r="Q10">
-        <v>0</v>
-      </c>
       <c r="R10">
         <v>0</v>
       </c>
@@ -1450,8 +1548,14 @@
       <c r="U10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:21">
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1497,26 +1601,32 @@
       <c r="O11" s="1">
         <v>22</v>
       </c>
-      <c r="P11">
-        <v>0</v>
-      </c>
-      <c r="Q11">
-        <v>0</v>
+      <c r="P11" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>22</v>
       </c>
       <c r="R11">
         <v>0</v>
       </c>
       <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
         <v>1</v>
       </c>
-      <c r="T11">
+      <c r="V11">
         <v>38</v>
       </c>
-      <c r="U11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" ht="93.75">
+      <c r="W11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" ht="75">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1562,11 +1672,11 @@
       <c r="O12" s="1">
         <v>22</v>
       </c>
-      <c r="P12">
-        <v>0</v>
-      </c>
-      <c r="Q12">
-        <v>0</v>
+      <c r="P12" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>22</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -1575,13 +1685,19 @@
         <v>0</v>
       </c>
       <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
         <v>43</v>
       </c>
-      <c r="U12">
+      <c r="W12">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="131.25">
+    <row r="13" spans="1:23" ht="112.5">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1627,11 +1743,11 @@
       <c r="O13" s="1">
         <v>22</v>
       </c>
-      <c r="P13">
-        <v>0</v>
-      </c>
-      <c r="Q13">
-        <v>0</v>
+      <c r="P13" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>22</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -1640,13 +1756,19 @@
         <v>0</v>
       </c>
       <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
         <v>44</v>
       </c>
-      <c r="U13">
+      <c r="W13">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="37.5">
+    <row r="14" spans="1:23" ht="37.5">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1692,11 +1814,11 @@
       <c r="O14" s="1">
         <v>22</v>
       </c>
-      <c r="P14">
-        <v>0</v>
-      </c>
-      <c r="Q14">
-        <v>0</v>
+      <c r="P14" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>22</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -1705,13 +1827,19 @@
         <v>0</v>
       </c>
       <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
         <v>46</v>
       </c>
-      <c r="U14">
+      <c r="W14">
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="168.75">
+    <row r="15" spans="1:23" ht="112.5">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1757,11 +1885,11 @@
       <c r="O15" s="1">
         <v>22</v>
       </c>
-      <c r="P15">
-        <v>0</v>
-      </c>
-      <c r="Q15">
-        <v>0</v>
+      <c r="P15" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q15" s="1">
+        <v>22</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -1770,13 +1898,19 @@
         <v>0</v>
       </c>
       <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
         <v>47</v>
       </c>
-      <c r="U15">
+      <c r="W15">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:21" ht="168.75">
+    <row r="16" spans="1:23" ht="131.25">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1822,11 +1956,11 @@
       <c r="O16" s="1">
         <v>22</v>
       </c>
-      <c r="P16">
-        <v>0</v>
-      </c>
-      <c r="Q16">
-        <v>0</v>
+      <c r="P16" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>22</v>
       </c>
       <c r="R16">
         <v>0</v>
@@ -1838,10 +1972,16 @@
         <v>0</v>
       </c>
       <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:21" ht="37.5">
+    <row r="17" spans="1:23">
       <c r="A17">
         <v>15</v>
       </c>
@@ -1887,26 +2027,32 @@
       <c r="O17" s="1">
         <v>22</v>
       </c>
-      <c r="P17">
-        <v>0</v>
-      </c>
-      <c r="Q17">
-        <v>0</v>
+      <c r="P17" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>22</v>
       </c>
       <c r="R17">
         <v>0</v>
       </c>
       <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
         <v>2</v>
       </c>
-      <c r="T17">
+      <c r="V17">
         <v>49</v>
       </c>
-      <c r="U17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:21">
+      <c r="W17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1924,8 +2070,10 @@
       <c r="M18" s="5"/>
       <c r="N18" s="1"/>
       <c r="O18" s="5"/>
-    </row>
-    <row r="19" spans="1:21">
+      <c r="P18" s="1"/>
+      <c r="Q18" s="5"/>
+    </row>
+    <row r="19" spans="1:23">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1934,67 +2082,67 @@
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
     </row>
-    <row r="20" spans="1:21">
+    <row r="20" spans="1:23">
       <c r="A20">
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:21">
+    <row r="21" spans="1:23">
       <c r="A21">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:21">
+    <row r="22" spans="1:23">
       <c r="A22">
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:21">
+    <row r="23" spans="1:23">
       <c r="A23">
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:21">
+    <row r="24" spans="1:23">
       <c r="A24">
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:21">
+    <row r="25" spans="1:23">
       <c r="A25">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:21">
+    <row r="26" spans="1:23">
       <c r="A26">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:21">
+    <row r="27" spans="1:23">
       <c r="A27">
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:21">
+    <row r="28" spans="1:23">
       <c r="A28">
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:21">
+    <row r="29" spans="1:23">
       <c r="A29">
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:21">
+    <row r="30" spans="1:23">
       <c r="A30">
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:21">
+    <row r="31" spans="1:23">
       <c r="A31">
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:21">
+    <row r="32" spans="1:23">
       <c r="A32">
         <v>30</v>
       </c>

--- a/Assets/Originals/Excels/System/SystemMessage.xlsx
+++ b/Assets/Originals/Excels/System/SystemMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD80C577-EE33-4EC7-8EAC-BBD053C29D49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8A5DC13-1C85-4BEA-BD18-ED33FA5A7985}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1099,7 +1099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="93.75">
+    <row r="4" spans="1:23" ht="56.25">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1433,7 +1433,7 @@
         <v>126</v>
       </c>
       <c r="Q8">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="R8">
         <v>0</v>

--- a/Assets/Originals/Excels/System/SystemMessage.xlsx
+++ b/Assets/Originals/Excels/System/SystemMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8A5DC13-1C85-4BEA-BD18-ED33FA5A7985}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A37D587-0002-4C2A-8FE3-88AE924E5E42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="151">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -551,6 +551,60 @@
   </si>
   <si>
     <t>Das Tutorial ist beendet</t>
+  </si>
+  <si>
+    <t>messageFrench</t>
+  </si>
+  <si>
+    <t>messageSizeFrench</t>
+  </si>
+  <si>
+    <t>Ici, c'est le monde éternel</t>
+  </si>
+  <si>
+    <t>Le monde où aboutissent ceux
+qui sont morts dans le monde des vivants</t>
+  </si>
+  <si>
+    <t>Dites-moi le nom que vous portiez
+dans le monde des vivants</t>
+  </si>
+  <si>
+    <t>Saisissez un nom de 2 à 10 caractères</t>
+  </si>
+  <si>
+    <t>Merci de me l'avoir dit</t>
+  </si>
+  <si>
+    <t>Et maintenant… ce nom, ici même, je vais…</t>
+  </si>
+  <si>
+    <t>… l'anéantir</t>
+  </si>
+  <si>
+    <t>Début du tutoriel</t>
+  </si>
+  <si>
+    <t>Déplacez le personnage et
+ouvrez le tiroir d'un clic gauche</t>
+  </si>
+  <si>
+    <t>Appuyez sur P, Z ou Échap pour ouvrir le menu pause → « Objets »
+→ « Documents » → « Tutoriel »</t>
+  </si>
+  <si>
+    <t>Clic gauche… ouvrir le tiroir</t>
+  </si>
+  <si>
+    <t>Appuyez sur P, Z ou Échap pour ouvrir le menu pause → « Objets »
+→ « Objets mystérieux » → « Marteau » ou « Corde »</t>
+  </si>
+  <si>
+    <t>Clic gauche… toucher l'Orbe bleu du Jugement
+Cliquez sur l'image de l'Objet mystérieux pour le choisir</t>
+  </si>
+  <si>
+    <t>Fin du tutoriel</t>
   </si>
 </sst>
 </file>
@@ -904,7 +958,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W52"/>
+  <dimension ref="A1:Y52"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="114.5" customWidth="1"/>
@@ -919,15 +973,17 @@
     <col min="15" max="15" width="20.625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="71.75" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="20.375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="27.25" customWidth="1"/>
-    <col min="19" max="19" width="26.625" customWidth="1"/>
-    <col min="20" max="20" width="22.25" customWidth="1"/>
-    <col min="21" max="21" width="23.875" customWidth="1"/>
-    <col min="22" max="22" width="24.125" customWidth="1"/>
-    <col min="23" max="23" width="14.625" customWidth="1"/>
+    <col min="18" max="18" width="58.25" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="27.25" customWidth="1"/>
+    <col min="21" max="21" width="26.625" customWidth="1"/>
+    <col min="22" max="22" width="22.25" customWidth="1"/>
+    <col min="23" max="23" width="23.875" customWidth="1"/>
+    <col min="24" max="24" width="24.125" customWidth="1"/>
+    <col min="25" max="25" width="14.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -980,25 +1036,31 @@
         <v>120</v>
       </c>
       <c r="R1" t="s">
+        <v>135</v>
+      </c>
+      <c r="S1" t="s">
+        <v>136</v>
+      </c>
+      <c r="T1" t="s">
         <v>1</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
         <v>2</v>
       </c>
-      <c r="T1" t="s">
+      <c r="V1" t="s">
         <v>3</v>
       </c>
-      <c r="U1" t="s">
+      <c r="W1" t="s">
         <v>4</v>
       </c>
-      <c r="V1" t="s">
+      <c r="X1" t="s">
         <v>5</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Y1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:23">
+    <row r="2" spans="1:25">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1009,12 +1071,6 @@
       <c r="E2">
         <v>0</v>
       </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="S2">
-        <v>0</v>
-      </c>
       <c r="T2">
         <v>0</v>
       </c>
@@ -1027,8 +1083,14 @@
       <c r="W2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:23">
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1080,11 +1142,11 @@
       <c r="Q3">
         <v>32</v>
       </c>
-      <c r="R3">
-        <v>0</v>
+      <c r="R3" s="2" t="s">
+        <v>137</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -1098,8 +1160,14 @@
       <c r="W3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:23" ht="56.25">
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" ht="75">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1151,11 +1219,11 @@
       <c r="Q4">
         <v>24</v>
       </c>
-      <c r="R4">
-        <v>0</v>
+      <c r="R4" s="3" t="s">
+        <v>138</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -1169,8 +1237,14 @@
       <c r="W4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:23" ht="37.5">
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" ht="37.5">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1222,15 +1296,15 @@
       <c r="Q5">
         <v>24</v>
       </c>
-      <c r="R5">
+      <c r="R5" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="S5">
+        <v>24</v>
+      </c>
+      <c r="T5">
         <v>1</v>
       </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
         <v>0</v>
       </c>
@@ -1240,8 +1314,14 @@
       <c r="W5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:23" ht="37.5">
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" ht="37.5">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1293,26 +1373,32 @@
       <c r="Q6">
         <v>24</v>
       </c>
-      <c r="R6">
+      <c r="R6" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="S6">
+        <v>24</v>
+      </c>
+      <c r="T6">
         <v>2</v>
       </c>
-      <c r="S6">
+      <c r="U6">
         <v>3</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>0</v>
-      </c>
       <c r="V6">
         <v>0</v>
       </c>
       <c r="W6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:23">
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1364,11 +1450,11 @@
       <c r="Q7">
         <v>32</v>
       </c>
-      <c r="R7">
-        <v>0</v>
+      <c r="R7" s="2" t="s">
+        <v>141</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -1382,8 +1468,14 @@
       <c r="W7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:23">
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1435,26 +1527,32 @@
       <c r="Q8">
         <v>30</v>
       </c>
-      <c r="R8">
-        <v>0</v>
+      <c r="R8" s="2" t="s">
+        <v>142</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
         <v>3</v>
       </c>
-      <c r="U8">
-        <v>0</v>
-      </c>
-      <c r="V8">
-        <v>0</v>
-      </c>
       <c r="W8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:23">
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1506,11 +1604,11 @@
       <c r="Q9">
         <v>32</v>
       </c>
-      <c r="R9">
-        <v>0</v>
+      <c r="R9" s="2" t="s">
+        <v>143</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -1524,8 +1622,14 @@
       <c r="W9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:23">
+      <c r="X9">
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1536,12 +1640,6 @@
       <c r="E10">
         <v>0</v>
       </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
-        <v>0</v>
-      </c>
       <c r="T10">
         <v>0</v>
       </c>
@@ -1554,8 +1652,14 @@
       <c r="W10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:23">
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1607,26 +1711,32 @@
       <c r="Q11" s="1">
         <v>22</v>
       </c>
-      <c r="R11">
-        <v>0</v>
-      </c>
-      <c r="S11">
-        <v>0</v>
+      <c r="R11" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="S11" s="1">
+        <v>22</v>
       </c>
       <c r="T11">
         <v>0</v>
       </c>
       <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
         <v>1</v>
       </c>
-      <c r="V11">
+      <c r="X11">
         <v>38</v>
       </c>
-      <c r="W11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23" ht="75">
+      <c r="Y11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" ht="75">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1678,11 +1788,11 @@
       <c r="Q12" s="1">
         <v>22</v>
       </c>
-      <c r="R12">
-        <v>0</v>
-      </c>
-      <c r="S12">
-        <v>0</v>
+      <c r="R12" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="S12" s="1">
+        <v>22</v>
       </c>
       <c r="T12">
         <v>0</v>
@@ -1691,13 +1801,19 @@
         <v>0</v>
       </c>
       <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
         <v>43</v>
       </c>
-      <c r="W12">
+      <c r="Y12">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:23" ht="112.5">
+    <row r="13" spans="1:25" ht="112.5">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1749,11 +1865,11 @@
       <c r="Q13" s="1">
         <v>22</v>
       </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
+      <c r="R13" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="S13" s="1">
+        <v>22</v>
       </c>
       <c r="T13">
         <v>0</v>
@@ -1762,13 +1878,19 @@
         <v>0</v>
       </c>
       <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
         <v>44</v>
       </c>
-      <c r="W13">
+      <c r="Y13">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="37.5">
+    <row r="14" spans="1:25" ht="37.5">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1820,11 +1942,11 @@
       <c r="Q14" s="1">
         <v>22</v>
       </c>
-      <c r="R14">
-        <v>0</v>
-      </c>
-      <c r="S14">
-        <v>0</v>
+      <c r="R14" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="S14" s="1">
+        <v>22</v>
       </c>
       <c r="T14">
         <v>0</v>
@@ -1833,13 +1955,19 @@
         <v>0</v>
       </c>
       <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
         <v>46</v>
       </c>
-      <c r="W14">
+      <c r="Y14">
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:23" ht="112.5">
+    <row r="15" spans="1:25" ht="131.25">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1891,11 +2019,11 @@
       <c r="Q15" s="1">
         <v>22</v>
       </c>
-      <c r="R15">
-        <v>0</v>
-      </c>
-      <c r="S15">
-        <v>0</v>
+      <c r="R15" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="S15" s="1">
+        <v>22</v>
       </c>
       <c r="T15">
         <v>0</v>
@@ -1904,13 +2032,19 @@
         <v>0</v>
       </c>
       <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
         <v>47</v>
       </c>
-      <c r="W15">
+      <c r="Y15">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="131.25">
+    <row r="16" spans="1:25" ht="131.25">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1962,11 +2096,11 @@
       <c r="Q16" s="1">
         <v>22</v>
       </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>0</v>
+      <c r="R16" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="S16" s="1">
+        <v>22</v>
       </c>
       <c r="T16">
         <v>0</v>
@@ -1978,10 +2112,16 @@
         <v>0</v>
       </c>
       <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:23">
+    <row r="17" spans="1:25">
       <c r="A17">
         <v>15</v>
       </c>
@@ -2033,26 +2173,32 @@
       <c r="Q17" s="1">
         <v>22</v>
       </c>
-      <c r="R17">
-        <v>0</v>
-      </c>
-      <c r="S17">
-        <v>0</v>
+      <c r="R17" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="S17" s="1">
+        <v>22</v>
       </c>
       <c r="T17">
         <v>0</v>
       </c>
       <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
         <v>2</v>
       </c>
-      <c r="V17">
+      <c r="X17">
         <v>49</v>
       </c>
-      <c r="W17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23">
+      <c r="Y17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25">
       <c r="A18">
         <v>16</v>
       </c>
@@ -2072,8 +2218,10 @@
       <c r="O18" s="5"/>
       <c r="P18" s="1"/>
       <c r="Q18" s="5"/>
-    </row>
-    <row r="19" spans="1:23">
+      <c r="R18" s="1"/>
+      <c r="S18" s="5"/>
+    </row>
+    <row r="19" spans="1:25">
       <c r="A19">
         <v>17</v>
       </c>
@@ -2082,67 +2230,67 @@
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
     </row>
-    <row r="20" spans="1:23">
+    <row r="20" spans="1:25">
       <c r="A20">
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:23">
+    <row r="21" spans="1:25">
       <c r="A21">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:23">
+    <row r="22" spans="1:25">
       <c r="A22">
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:23">
+    <row r="23" spans="1:25">
       <c r="A23">
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:23">
+    <row r="24" spans="1:25">
       <c r="A24">
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:23">
+    <row r="25" spans="1:25">
       <c r="A25">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:23">
+    <row r="26" spans="1:25">
       <c r="A26">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:23">
+    <row r="27" spans="1:25">
       <c r="A27">
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:23">
+    <row r="28" spans="1:25">
       <c r="A28">
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:23">
+    <row r="29" spans="1:25">
       <c r="A29">
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:23">
+    <row r="30" spans="1:25">
       <c r="A30">
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:23">
+    <row r="31" spans="1:25">
       <c r="A31">
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:23">
+    <row r="32" spans="1:25">
       <c r="A32">
         <v>30</v>
       </c>

--- a/Assets/Originals/Excels/System/SystemMessage.xlsx
+++ b/Assets/Originals/Excels/System/SystemMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A37D587-0002-4C2A-8FE3-88AE924E5E42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACC732B6-2E77-4379-B333-DFD5D1E87AE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -553,12 +553,6 @@
     <t>Das Tutorial ist beendet</t>
   </si>
   <si>
-    <t>messageFrench</t>
-  </si>
-  <si>
-    <t>messageSizeFrench</t>
-  </si>
-  <si>
     <t>Ici, c'est le monde éternel</t>
   </si>
   <si>
@@ -605,6 +599,14 @@
   </si>
   <si>
     <t>Fin du tutoriel</t>
+  </si>
+  <si>
+    <t>messageSizeFrench</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>messageFrench</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -1036,10 +1038,10 @@
         <v>120</v>
       </c>
       <c r="R1" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="S1" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="T1" t="s">
         <v>1</v>
@@ -1143,7 +1145,7 @@
         <v>32</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="S3">
         <v>32</v>
@@ -1167,7 +1169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="75">
+    <row r="4" spans="1:25" ht="56.25">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1220,7 +1222,7 @@
         <v>24</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="S4">
         <v>24</v>
@@ -1297,7 +1299,7 @@
         <v>24</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="S5">
         <v>24</v>
@@ -1374,7 +1376,7 @@
         <v>24</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="S6">
         <v>24</v>
@@ -1451,7 +1453,7 @@
         <v>32</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="S7">
         <v>32</v>
@@ -1528,7 +1530,7 @@
         <v>30</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="S8">
         <v>32</v>
@@ -1605,7 +1607,7 @@
         <v>32</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="S9">
         <v>32</v>
@@ -1712,7 +1714,7 @@
         <v>22</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="S11" s="1">
         <v>22</v>
@@ -1789,7 +1791,7 @@
         <v>22</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="S12" s="1">
         <v>22</v>
@@ -1866,7 +1868,7 @@
         <v>22</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="S13" s="1">
         <v>22</v>
@@ -1943,7 +1945,7 @@
         <v>22</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="S14" s="1">
         <v>22</v>
@@ -1967,7 +1969,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="131.25">
+    <row r="15" spans="1:25" ht="112.5">
       <c r="A15">
         <v>13</v>
       </c>
@@ -2020,7 +2022,7 @@
         <v>22</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="S15" s="1">
         <v>22</v>
@@ -2097,7 +2099,7 @@
         <v>22</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="S16" s="1">
         <v>22</v>
@@ -2174,7 +2176,7 @@
         <v>22</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="S17" s="1">
         <v>22</v>

--- a/Assets/Originals/Excels/System/SystemMessage.xlsx
+++ b/Assets/Originals/Excels/System/SystemMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACC732B6-2E77-4379-B333-DFD5D1E87AE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4955BCE5-BCB1-4DFB-83BE-5B60194C7DC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="167">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -607,6 +607,60 @@
   <si>
     <t>messageFrench</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>messageTurkish</t>
+  </si>
+  <si>
+    <t>messageSizeTurkish</t>
+  </si>
+  <si>
+    <t>Burası Ebedî Dünya</t>
+  </si>
+  <si>
+    <t>Yaşayanlar dünyasında ölenlerin
+sonunda vardığı dünya</t>
+  </si>
+  <si>
+    <t>Lütfen yaşayanlar dünyasında
+kullandığın adı söyle</t>
+  </si>
+  <si>
+    <t>2 ile 10 karakter arasında bir ad gir</t>
+  </si>
+  <si>
+    <t>Söylediğin için teşekkür ederim</t>
+  </si>
+  <si>
+    <t>Ve şimdi… adını burada, hemen…</t>
+  </si>
+  <si>
+    <t>…yok ediyorum</t>
+  </si>
+  <si>
+    <t>Eğitim başlıyor</t>
+  </si>
+  <si>
+    <t>Karakteri hareket ettir ve
+sol tıkla çekmeceyi aç</t>
+  </si>
+  <si>
+    <t>P, Z veya ESC ile duraklatma menüsünü aç → “Eşyalar”
+→ “Belgeler” → “Eğitim”</t>
+  </si>
+  <si>
+    <t>Sol tık… Çekmeceyi aç</t>
+  </si>
+  <si>
+    <t>P, Z veya ESC ile duraklatma menüsünü aç → “Eşyalar”
+→ “Gizemli Eşyalar” → “Çekiç” veya “İp”</t>
+  </si>
+  <si>
+    <t>Sol tık… Yargının Mavi Küresi'ne dokun
+Gizemli Eşyanın resmini sol tıkla seç</t>
+  </si>
+  <si>
+    <t>Eğitim tamamlandı</t>
   </si>
 </sst>
 </file>
@@ -960,7 +1014,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y52"/>
+  <dimension ref="A1:AA52"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="114.5" customWidth="1"/>
@@ -977,15 +1031,17 @@
     <col min="17" max="17" width="20.375" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="58.25" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="19.5" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="27.25" customWidth="1"/>
-    <col min="21" max="21" width="26.625" customWidth="1"/>
-    <col min="22" max="22" width="22.25" customWidth="1"/>
-    <col min="23" max="23" width="23.875" customWidth="1"/>
-    <col min="24" max="24" width="24.125" customWidth="1"/>
-    <col min="25" max="25" width="14.625" customWidth="1"/>
+    <col min="20" max="20" width="48.375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="20.125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="27.25" customWidth="1"/>
+    <col min="23" max="23" width="26.625" customWidth="1"/>
+    <col min="24" max="24" width="22.25" customWidth="1"/>
+    <col min="25" max="25" width="23.875" customWidth="1"/>
+    <col min="26" max="26" width="24.125" customWidth="1"/>
+    <col min="27" max="27" width="14.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:27">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1044,25 +1100,31 @@
         <v>149</v>
       </c>
       <c r="T1" t="s">
+        <v>151</v>
+      </c>
+      <c r="U1" t="s">
+        <v>152</v>
+      </c>
+      <c r="V1" t="s">
         <v>1</v>
       </c>
-      <c r="U1" t="s">
+      <c r="W1" t="s">
         <v>2</v>
       </c>
-      <c r="V1" t="s">
+      <c r="X1" t="s">
         <v>3</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Y1" t="s">
         <v>4</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Z1" t="s">
         <v>5</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AA1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:27">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1073,12 +1135,6 @@
       <c r="E2">
         <v>0</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
-      <c r="U2">
-        <v>0</v>
-      </c>
       <c r="V2">
         <v>0</v>
       </c>
@@ -1091,8 +1147,14 @@
       <c r="Y2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:25">
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1150,11 +1212,11 @@
       <c r="S3">
         <v>32</v>
       </c>
-      <c r="T3">
-        <v>0</v>
+      <c r="T3" s="2" t="s">
+        <v>153</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="V3">
         <v>0</v>
@@ -1168,8 +1230,14 @@
       <c r="Y3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:25" ht="56.25">
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" ht="56.25">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1227,11 +1295,11 @@
       <c r="S4">
         <v>24</v>
       </c>
-      <c r="T4">
-        <v>0</v>
+      <c r="T4" s="3" t="s">
+        <v>154</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V4">
         <v>0</v>
@@ -1245,8 +1313,14 @@
       <c r="Y4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:25" ht="37.5">
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" ht="37.5">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1304,15 +1378,15 @@
       <c r="S5">
         <v>24</v>
       </c>
-      <c r="T5">
+      <c r="T5" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="U5">
+        <v>24</v>
+      </c>
+      <c r="V5">
         <v>1</v>
       </c>
-      <c r="U5">
-        <v>0</v>
-      </c>
-      <c r="V5">
-        <v>0</v>
-      </c>
       <c r="W5">
         <v>0</v>
       </c>
@@ -1322,8 +1396,14 @@
       <c r="Y5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:25" ht="37.5">
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" ht="37.5">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1381,26 +1461,32 @@
       <c r="S6">
         <v>24</v>
       </c>
-      <c r="T6">
+      <c r="T6" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="U6">
+        <v>24</v>
+      </c>
+      <c r="V6">
         <v>2</v>
       </c>
-      <c r="U6">
+      <c r="W6">
         <v>3</v>
       </c>
-      <c r="V6">
-        <v>0</v>
-      </c>
-      <c r="W6">
-        <v>0</v>
-      </c>
       <c r="X6">
         <v>0</v>
       </c>
       <c r="Y6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:25">
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1458,11 +1544,11 @@
       <c r="S7">
         <v>32</v>
       </c>
-      <c r="T7">
-        <v>0</v>
+      <c r="T7" s="2" t="s">
+        <v>157</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="V7">
         <v>0</v>
@@ -1476,8 +1562,14 @@
       <c r="Y7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:25">
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1535,26 +1627,32 @@
       <c r="S8">
         <v>32</v>
       </c>
-      <c r="T8">
-        <v>0</v>
+      <c r="T8" s="2" t="s">
+        <v>158</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
         <v>3</v>
       </c>
-      <c r="W8">
-        <v>0</v>
-      </c>
-      <c r="X8">
-        <v>0</v>
-      </c>
       <c r="Y8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:25">
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1612,11 +1710,11 @@
       <c r="S9">
         <v>32</v>
       </c>
-      <c r="T9">
-        <v>0</v>
+      <c r="T9" s="2" t="s">
+        <v>159</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="V9">
         <v>0</v>
@@ -1630,8 +1728,14 @@
       <c r="Y9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:25">
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1642,12 +1746,6 @@
       <c r="E10">
         <v>0</v>
       </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
-      <c r="U10">
-        <v>0</v>
-      </c>
       <c r="V10">
         <v>0</v>
       </c>
@@ -1660,8 +1758,14 @@
       <c r="Y10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:25">
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1719,26 +1823,32 @@
       <c r="S11" s="1">
         <v>22</v>
       </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
-      <c r="U11">
-        <v>0</v>
+      <c r="T11" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="U11" s="1">
+        <v>22</v>
       </c>
       <c r="V11">
         <v>0</v>
       </c>
       <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>0</v>
+      </c>
+      <c r="Y11">
         <v>1</v>
       </c>
-      <c r="X11">
+      <c r="Z11">
         <v>38</v>
       </c>
-      <c r="Y11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25" ht="75">
+      <c r="AA11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" ht="75">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1796,11 +1906,11 @@
       <c r="S12" s="1">
         <v>22</v>
       </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
-      <c r="U12">
-        <v>0</v>
+      <c r="T12" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="U12" s="1">
+        <v>22</v>
       </c>
       <c r="V12">
         <v>0</v>
@@ -1809,13 +1919,19 @@
         <v>0</v>
       </c>
       <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
         <v>43</v>
       </c>
-      <c r="Y12">
+      <c r="AA12">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="112.5">
+    <row r="13" spans="1:27" ht="112.5">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1873,11 +1989,11 @@
       <c r="S13" s="1">
         <v>22</v>
       </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>0</v>
+      <c r="T13" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="U13" s="1">
+        <v>22</v>
       </c>
       <c r="V13">
         <v>0</v>
@@ -1886,13 +2002,19 @@
         <v>0</v>
       </c>
       <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
         <v>44</v>
       </c>
-      <c r="Y13">
+      <c r="AA13">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="37.5">
+    <row r="14" spans="1:27" ht="37.5">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1950,11 +2072,11 @@
       <c r="S14" s="1">
         <v>22</v>
       </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
-      <c r="U14">
-        <v>0</v>
+      <c r="T14" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="U14" s="1">
+        <v>22</v>
       </c>
       <c r="V14">
         <v>0</v>
@@ -1963,13 +2085,19 @@
         <v>0</v>
       </c>
       <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
         <v>46</v>
       </c>
-      <c r="Y14">
+      <c r="AA14">
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="112.5">
+    <row r="15" spans="1:27" ht="112.5">
       <c r="A15">
         <v>13</v>
       </c>
@@ -2027,11 +2155,11 @@
       <c r="S15" s="1">
         <v>22</v>
       </c>
-      <c r="T15">
-        <v>0</v>
-      </c>
-      <c r="U15">
-        <v>0</v>
+      <c r="T15" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="U15" s="1">
+        <v>22</v>
       </c>
       <c r="V15">
         <v>0</v>
@@ -2040,13 +2168,19 @@
         <v>0</v>
       </c>
       <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
         <v>47</v>
       </c>
-      <c r="Y15">
+      <c r="AA15">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="131.25">
+    <row r="16" spans="1:27" ht="131.25">
       <c r="A16">
         <v>14</v>
       </c>
@@ -2104,11 +2238,11 @@
       <c r="S16" s="1">
         <v>22</v>
       </c>
-      <c r="T16">
-        <v>0</v>
-      </c>
-      <c r="U16">
-        <v>0</v>
+      <c r="T16" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="U16" s="1">
+        <v>22</v>
       </c>
       <c r="V16">
         <v>0</v>
@@ -2120,10 +2254,16 @@
         <v>0</v>
       </c>
       <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:25">
+    <row r="17" spans="1:27">
       <c r="A17">
         <v>15</v>
       </c>
@@ -2181,26 +2321,32 @@
       <c r="S17" s="1">
         <v>22</v>
       </c>
-      <c r="T17">
-        <v>0</v>
-      </c>
-      <c r="U17">
-        <v>0</v>
+      <c r="T17" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="U17" s="1">
+        <v>22</v>
       </c>
       <c r="V17">
         <v>0</v>
       </c>
       <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
         <v>2</v>
       </c>
-      <c r="X17">
+      <c r="Z17">
         <v>49</v>
       </c>
-      <c r="Y17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:25">
+      <c r="AA17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27">
       <c r="A18">
         <v>16</v>
       </c>
@@ -2222,8 +2368,10 @@
       <c r="Q18" s="5"/>
       <c r="R18" s="1"/>
       <c r="S18" s="5"/>
-    </row>
-    <row r="19" spans="1:25">
+      <c r="T18" s="1"/>
+      <c r="U18" s="5"/>
+    </row>
+    <row r="19" spans="1:27">
       <c r="A19">
         <v>17</v>
       </c>
@@ -2232,67 +2380,67 @@
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
     </row>
-    <row r="20" spans="1:25">
+    <row r="20" spans="1:27">
       <c r="A20">
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:25">
+    <row r="21" spans="1:27">
       <c r="A21">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:25">
+    <row r="22" spans="1:27">
       <c r="A22">
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:25">
+    <row r="23" spans="1:27">
       <c r="A23">
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:25">
+    <row r="24" spans="1:27">
       <c r="A24">
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:25">
+    <row r="25" spans="1:27">
       <c r="A25">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:25">
+    <row r="26" spans="1:27">
       <c r="A26">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:25">
+    <row r="27" spans="1:27">
       <c r="A27">
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:25">
+    <row r="28" spans="1:27">
       <c r="A28">
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:25">
+    <row r="29" spans="1:27">
       <c r="A29">
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:25">
+    <row r="30" spans="1:27">
       <c r="A30">
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:25">
+    <row r="31" spans="1:27">
       <c r="A31">
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:25">
+    <row r="32" spans="1:27">
       <c r="A32">
         <v>30</v>
       </c>
